--- a/Flujo de Efectivo/Optimizacion de pagos.xlsx
+++ b/Flujo de Efectivo/Optimizacion de pagos.xlsx
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>7957.57</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="17">
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>15370</v>
       </c>
     </row>
     <row r="18">
@@ -626,7 +626,7 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0</v>
+        <v>16240</v>
       </c>
     </row>
     <row r="19">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>0</v>
+        <v>19888.8</v>
       </c>
     </row>
     <row r="20">
